--- a/proyectos.xlsx
+++ b/proyectos.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>proyecto</t>
   </si>
@@ -51,6 +51,9 @@
     <t>2025-01-10</t>
   </si>
   <si>
+    <t>2025-09-30</t>
+  </si>
+  <si>
     <t>Acabados</t>
   </si>
   <si>
@@ -66,6 +69,9 @@
     <t>2025-02-15</t>
   </si>
   <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
     <t>Estructura</t>
   </si>
   <si>
@@ -79,6 +85,9 @@
   </si>
   <si>
     <t>2025-03-01</t>
+  </si>
+  <si>
+    <t>2025-08-15</t>
   </si>
   <si>
     <t>Acabados finales</t>
@@ -124,9 +133,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11.0"/>
@@ -154,15 +160,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -420,8 +423,8 @@
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3">
-        <v>46295.0</v>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D2" s="1">
         <v>72.0</v>
@@ -430,13 +433,13 @@
         <v>75.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1">
         <v>3.2E8</v>
@@ -444,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46721.0</v>
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D3" s="1">
         <v>45.0</v>
@@ -459,13 +462,13 @@
         <v>50.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1">
         <v>2.8E8</v>
@@ -473,13 +476,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="3">
-        <v>46614.0</v>
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D4" s="1">
         <v>88.0</v>
@@ -488,13 +491,13 @@
         <v>85.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I4" s="1">
         <v>1.95E8</v>
@@ -502,13 +505,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1">
         <v>20.0</v>
@@ -517,13 +520,13 @@
         <v>25.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I5" s="1">
         <v>4.1E8</v>
@@ -531,13 +534,13 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1">
         <v>8.0</v>
@@ -546,13 +549,13 @@
         <v>10.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I6" s="1">
         <v>3.5E8</v>
